--- a/build/simple-flow/SimpleFlow_TraceabilityStatus_2026-07-22.xlsx
+++ b/build/simple-flow/SimpleFlow_TraceabilityStatus_2026-07-22.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>184 cases in scope · 180 Traceable (per-story ticket set in TestRail refs) · 4 flagged (id-map C-ID absent in live TestRail). Spec anchor: https://shopview.atlassian.net/wiki/spaces/PM/pages/646021121</t>
+          <t>184 cases in scope · 180 Traceable (per-story ticket + spec anchor together in TestRail refs) · 4 ignored per user 2026-07-22 (id-map C-ID absent in live TestRail). Spec: https://shopview.atlassian.net/wiki/spaces/PM/pages/646021121</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ticket refs (set)</t>
+          <t>refs — ticket + spec (set)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R1)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R2 / S8-R3)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R4)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R5)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R6)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>SV-7703, SV-7705</t>
+          <t>SV-7703,SV-7705 (S8-R7 / S10-R3)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R8)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R10)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R11)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R5)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>SV-7697</t>
+          <t>SV-7697 (S2-R1)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>SV-7697</t>
+          <t>SV-7697 (S2-R2 / S2-R3 / S2-R4)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>SV-7697, SV-7710</t>
+          <t>SV-7697,SV-7710 (S2-R4 / S2-R5 / S15-R3)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>SV-7697, SV-7710</t>
+          <t>SV-7697,SV-7710 (S2-R5 / S15-R3)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>SV-7697</t>
+          <t>SV-7697 (S2-R2 / S2 AC (missing required fields blocked))</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>SV-7697</t>
+          <t>SV-7697 (S2-R6 / S2 AC (Create POs off ⇒ no PO))</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>FLAGGED — TestRail case absent (refs recorded locally only)</t>
+          <t>IGNORED per user (TestRail case absent; refs kept locally)</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SV-7697</t>
+          <t>SV-7697 (S2-R6 / §5 invariant 1)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>SV-7697</t>
+          <t>SV-7697 (S2-R2 / S2 AC (auto-pick off ⇒ pick in modal))</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>SV-7697, SV-7870</t>
+          <t>SV-7697,SV-7870 (S2-R6 / S2 AC (re-open returns to Approved); S16-R12 (auto-complete on re-resolve))</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>SV-7697</t>
+          <t>SV-7697 (S2 AC (individual-line Complete + per-part receive kept))</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R4)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R1 / S3-R2 / S3-R9)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R5)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R6)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R7 / S3-R9 (Cancel idempotent))</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R3)</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R8)</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>SV-7699</t>
+          <t>SV-7699 (S4-R4)</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>SV-7699</t>
+          <t>SV-7699 (S4-R5 / S4-R7)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>SV-7699</t>
+          <t>SV-7699 (S4-R6)</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7699</t>
+          <t>SV-7698,SV-7699 (S4-R8 / Key Decision (all lines approved) / S3-R9)</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>SV-7699</t>
+          <t>SV-7699 (S4-R8 / Key Decision (holds regardless of Auto-approve))</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R9 (no duplicate POs on re-Complete))</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7699</t>
+          <t>SV-7698,SV-7699 (S3-C1 / S4-C1 / Resolve Cores handoff)</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-C1 (skipped if none))</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R1/C-R4)</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R4)</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R6)</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R2/C-R4 (guardrail))</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (Resolve Cores handoff (live +$ total))</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>SV-7704</t>
+          <t>SV-7704 (S9-R1)</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>SV-7704</t>
+          <t>SV-7704 (S9-R2)</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>SV-7704</t>
+          <t>SV-7704 (S9-R3)</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1 AC / §8 Permissions)</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>SV-8183</t>
+          <t>SV-8183 (§8 Permissions)</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>SV-8183</t>
+          <t>SV-8183 (§8 Permissions)</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>SV-8183</t>
+          <t>SV-8183 (R7 / §8 role-gating review)</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>SV-7706</t>
+          <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>SV-8183</t>
+          <t>SV-8183 (§8 BE enforcement)</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>SV-8183</t>
+          <t>SV-8183 (§8 role-gating review)</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>SV-8183</t>
+          <t>SV-8183 (R7 (review sign-off) — self-review permission-gated (identity rule NOT in v1))</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>SV-7700</t>
+          <t>SV-7700 (S5 / §9 (See Financial Data gate))</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>SV-8183</t>
+          <t>SV-8183 (§9 per-role completion matrix)</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>SV-7705</t>
+          <t>SV-7705 (S10-R1)</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>SV-7705</t>
+          <t>SV-7705 (S10-R1 (PN mandatory to receive); S10-R2 struck (first-class part not required in v1))</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>SV-7705</t>
+          <t>SV-7705 (S10-R1 (PN mandatory to receive); S10-R2 struck (linking to first-class item not required in v1))</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>SV-7703, SV-7705</t>
+          <t>SV-7703,SV-7705 (S10-R2 / S8-R7)</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>SV-7705, SV-7708</t>
+          <t>SV-7705,SV-7708 (S10 Negative / S13-R6 / S13-R7)</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>SV-7705</t>
+          <t>SV-7705 (S10-R1 + S10 technical guardrails; S10-R2 struck (catalog/inventory creation not required in v1))</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>SV-7702</t>
+          <t>SV-7702 (S7-R1)</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>SV-7702</t>
+          <t>SV-7702 (S7-R2)</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>SV-7702</t>
+          <t>SV-7702 (S7-R3)</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>SV-7702</t>
+          <t>SV-7702 (S7-R4)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>SV-7702</t>
+          <t>SV-7702 (S7-R5)</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>SV-7702</t>
+          <t>SV-7702 (S7 (select-all scope))</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>SV-7301</t>
+          <t>SV-7301 (§5 invariant 1)</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (§5 / §4 (Create POs OFF))</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>FLAGGED — TestRail case absent (refs recorded locally only)</t>
+          <t>IGNORED per user (TestRail case absent; refs kept locally)</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>SV-7301</t>
+          <t>SV-7301 (§5 invariant 2)</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (§5 (vendorless/no-PN))</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (§5 / S6-R3)</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>SV-7301</t>
+          <t>SV-7301 (§8 (cost at completion))</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>SV-7301</t>
+          <t>SV-7301 (§5 (Journal Entry / Inventory → QBO))</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>SV-7705</t>
+          <t>SV-7705 (§5 invariant 3 (rescoped after S10-R2 strike))</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>SV-7706</t>
+          <t>SV-7706 (S11-R1)</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>SV-7706</t>
+          <t>SV-7706 (S11-R2)</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>SV-7706</t>
+          <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>SV-7707</t>
+          <t>SV-7707 (S12 (existing multi-vendor))</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>SV-7707</t>
+          <t>SV-7707 (S12-R1 (+ Milos Round-3 2026-07-16))</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>SV-7707, SV-7708</t>
+          <t>SV-7707,SV-7708 (S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>SV-7707</t>
+          <t>SV-7707 (S12-R3 (+ Milos Round-3 2026-07-16))</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>SV-7707</t>
+          <t>SV-7707 (S12-R4)</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>SV-7707</t>
+          <t>SV-7707 (S12 (existing) received-more-than-ordered)</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R1 + S16-R12)</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R2)</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R3)</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R4)</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R5 / R6 + S16-R12)</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R7 / R10)</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R6)</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R5 / R8 (direct sign-off, no separate Complete) + S16-R12)</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R7 (role-gating))</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R7 (VIN required, no note))</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R8 + S16-R12)</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R9)</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R11)</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>SV-7870, SV-8353</t>
+          <t>SV-7870,SV-8353 (S18 / Story 16 core paragraph)</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R Open (default) - Milos Round-3 2026-07-16: ON for new orgs)</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R1..R8 / Story 1 AC)</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1 AC / Key Decision (no operatingMode))</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R2 (Create purchase orders))</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>FLAGGED — TestRail case absent (refs recorded locally only)</t>
+          <t>IGNORED per user (TestRail case absent; refs kept locally)</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R3 (Vendor invoice Optional/Required))</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R1 (Auto-approve ON))</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R1 (Auto-approve OFF))</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R5..R8 (existing settings surfaced))</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1 first-use defaults / §4)</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>FLAGGED — TestRail case absent (refs recorded locally only)</t>
+          <t>IGNORED per user (TestRail case absent; refs kept locally)</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R9 (Save persists org-wide))</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R9 (future completions + apply on reopen; never retroactive to WOs left completed))</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1 AC (non-admin can't see/modify))</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1 AC (no requireVin / no operatingMode field))</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1 (Save dirty-state))</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1-R4 (Require review before completion))</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>SV-7696</t>
+          <t>SV-7696 (S1 AC (helper text per toggle))</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>SV-7876</t>
+          <t>SV-7876 (TS-R1)</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>SV-7876</t>
+          <t>SV-7876 (TS-R2)</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>SV-7876</t>
+          <t>SV-7876 (TS-R3)</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>SV-7876</t>
+          <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>SV-7876</t>
+          <t>SV-7876 (TS-R4 (multi-line navigation))</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>SV-7876</t>
+          <t>SV-7876 (TS-R5)</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>SV-7876</t>
+          <t>SV-7876 (TS-R6 (test id))</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>SV-7710</t>
+          <t>SV-7710 (TS Decision vs S15-R2)</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>SV-7710</t>
+          <t>SV-7710 (S15-R1)</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>SV-7710</t>
+          <t>SV-7710 (S15-R2)</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>SV-7710</t>
+          <t>SV-7710 (S15-R3)</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>SV-7710</t>
+          <t>SV-7710 (S15-R4)</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>SV-7697, SV-7698, SV-7699</t>
+          <t>SV-7697,SV-7698,SV-7699 (S2-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7699, SV-7710</t>
+          <t>SV-7698,SV-7699,SV-7710 (S15-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7699</t>
+          <t>SV-7698,SV-7699 (S3-R3 / S4-R3)</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>SV-7876</t>
+          <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7699</t>
+          <t>SV-7698,SV-7699 (S3-R3 / S4-R5 / §4)</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>SV-7705, SV-7707, SV-7708</t>
+          <t>SV-7705,SV-7707,SV-7708 (S10 / S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (R7)</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>SV-7698</t>
+          <t>SV-7698 (S3-R9 (idempotency))</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8-R7 / §4 field locking)</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>SV-7704</t>
+          <t>SV-7704 (S9-R3 / §4 (uniqueness relaxed))</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7699</t>
+          <t>SV-7698,SV-7699 (S4-R8 / S3-R9 / Key Decision (line approval))</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>SV-7708</t>
+          <t>SV-7708 (S13-R1)</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>SV-7708</t>
+          <t>SV-7708 (S13-R2)</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>SV-7708</t>
+          <t>SV-7708 (S13-R3)</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>SV-7708</t>
+          <t>SV-7708 (S13-R4 / S13-R5 / S13-R6 / S13-R7)</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>SV-7708</t>
+          <t>SV-7708 (S13 Technical guardrails)</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (S6-R1)</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (S6-R2)</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (S6-R3)</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (S6-R4)</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (S6-R5)</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (S6-R6)</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>SV-7700</t>
+          <t>SV-7700 (S5-R1)</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>SV-7700</t>
+          <t>SV-7700 (S5-R1 / S5 AC (validation))</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>SV-7700</t>
+          <t>SV-7700 (S5-R2)</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>SV-7700</t>
+          <t>SV-7700 (S5-R3)</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>SV-7700</t>
+          <t>SV-7700 (S5-R4 / S5 AC (no inventory interaction))</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>SV-7700</t>
+          <t>SV-7700 (S5 AC (transitions out of vendorless))</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>SV-7700</t>
+          <t>SV-7700 (S5-R4 / S5 AC (receive gate))</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>SV-7709</t>
+          <t>SV-7709 (S14-R1)</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>SV-7709</t>
+          <t>SV-7709 (S14-R2)</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>SV-7709</t>
+          <t>SV-7709 (S14-R3)</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>SV-7701</t>
+          <t>SV-7701 (S6-R7)</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>SV-7707</t>
+          <t>SV-7707 (S12-R5)</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>SV-7708</t>
+          <t>SV-7708 (S13-R7)</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (S16-R12 (a) single line)</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (S16-R12 (b) bulk)</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (S16-R12 (c) split)</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (S16-R12 (d) delete line)</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (S16-R12 review ON)</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (S16-R13 clock-out exception)</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>SV-7870</t>
+          <t>SV-7870 (S16-R12 backend status transition)</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R1)</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R3)</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R4)</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R5)</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R8)</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R9)</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 AC (resolution immutable with an active invoice))</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R2 / technical plan)</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>SV-8353</t>
+          <t>SV-8353 (S18 C-R10)</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7706</t>
+          <t>SV-7698,SV-7706 (S11-R4 (+ S3-R5 amendment))</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>SV-7707</t>
+          <t>SV-7707 (S12-R6)</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>SV-7707</t>
+          <t>SV-7707 (S12-R6)</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>SV-7708</t>
+          <t>SV-7708 (S13-R8 (SV-8343))</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>SV-7708</t>
+          <t>SV-7708 (S13-R8 (SV-8343))</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>SV-7702</t>
+          <t>SV-7702 (S7 AC (part-sale POs) + §8 Part Sales — confirmed)</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>SV-7703</t>
+          <t>SV-7703 (S8 AC (part-sale POs) + §8 Part Sales — confirmed)</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>SV-7709</t>
+          <t>SV-7709 (§8 Part Sales — confirmed (remaining check))</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>SV-7702, SV-7703</t>
+          <t>SV-7702,SV-7703 (§8 Part Sales — confirmed (Jul 14) + S7/S8 part-sale AC)</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
